--- a/29_Fund_of_Funds/_template_FOF.xlsx
+++ b/29_Fund_of_Funds/_template_FOF.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Underlying Fund Portfolio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="NAV Rollforward &amp; Fee Layering" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Performance &amp; Multiples" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Checks" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Sources" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="RefreshLog" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Underlying Fund Portfolio" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NAV Rollforward &amp; Fee Layering" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance &amp; Multiples" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RefreshLog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
     </row>

--- a/29_Fund_of_Funds/_template_FOF.xlsx
+++ b/29_Fund_of_Funds/_template_FOF.xlsx
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
     </row>

--- a/29_Fund_of_Funds/_template_FOF.xlsx
+++ b/29_Fund_of_Funds/_template_FOF.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Underlying Fund Portfolio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="NAV Rollforward &amp; Fee Layering" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Performance &amp; Multiples" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Checks" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Sources" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="RefreshLog" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Underlying Fund Portfolio" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NAV Rollforward &amp; Fee Layering" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance &amp; Multiples" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RefreshLog" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>

--- a/29_Fund_of_Funds/_template_FOF.xlsx
+++ b/29_Fund_of_Funds/_template_FOF.xlsx
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
     </row>

--- a/29_Fund_of_Funds/_template_FOF.xlsx
+++ b/29_Fund_of_Funds/_template_FOF.xlsx
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>C5+C6-C7-C8-C9+C10</f>
+        <f>C5+C6-C7-IF(ISBLANK(C14),C8,C14)-C9+C10</f>
         <v/>
       </c>
     </row>
@@ -3224,6 +3224,14 @@
         <f>C11-C12</f>
         <v/>
       </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>- Disclosed net investment loss (supersedes modelled fee when sourced)</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
